--- a/output/pdf_financials_xlsx/SGZ.xlsx
+++ b/output/pdf_financials_xlsx/SGZ.xlsx
@@ -6713,40 +6713,40 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.011151</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.726066</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.477619</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.377899</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.470991</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.463115</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.567452</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.472424</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.521435</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.18574</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.204868</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.194855</v>
       </c>
     </row>
     <row r="93">
@@ -11053,7 +11053,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12949,7 +12953,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGZ.xlsx
+++ b/output/pdf_financials_xlsx/SGZ.xlsx
@@ -2689,40 +2689,40 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001611</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003563</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008077000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.02901</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.265377</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.015886</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.300733</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.334885</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.243212</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.008703000000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.097069</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.004231</v>
       </c>
     </row>
     <row r="35">
@@ -2825,40 +2825,40 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001611</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003563</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.008077000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.02901</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.265377</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.015886</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.300733</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.334885</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.243212</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.008703000000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.097069</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.004231</v>
       </c>
     </row>
     <row r="37">
@@ -3641,40 +3641,40 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.067055</v>
+        <v>0.065444</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016318</v>
+        <v>0.012755</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.021406</v>
+        <v>0.013329</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.034595</v>
+        <v>0.005585</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.320675</v>
+        <v>0.055298</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.050864</v>
+        <v>0.034978</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.496744</v>
+        <v>0.196011</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.5055269999999999</v>
+        <v>0.170642</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.392505</v>
+        <v>0.149293</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.070372</v>
+        <v>0.061669</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.147314</v>
+        <v>0.050245</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.023441</v>
+        <v>0.01921</v>
       </c>
     </row>
     <row r="49">
@@ -8848,16 +8848,16 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011226</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026271</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02788</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017385</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -8916,16 +8916,16 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011226</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026271</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02788</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017385</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10278,7 +10278,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -16462,7 +16466,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16656,7 +16664,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGZ.xlsx
+++ b/output/pdf_financials_xlsx/SGZ.xlsx
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -9608,7 +9608,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>-0.09876699999999999</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.408032</v>
+        <v>-0.412532</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.145416</v>
@@ -17272,7 +17272,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
